--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488292_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488292_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7527</v>
+        <v>10.6121</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2503</v>
+        <v>7.0112</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5024</v>
+        <v>3.6009</v>
       </c>
       <c r="G2" t="n">
         <v>8.2994</v>
@@ -610,13 +610,13 @@
         <v>3.1499</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6966</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3209</v>
+        <v>0.0818</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0175</v>
+        <v>-0.919</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2297</v>
+        <v>4.9573</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8834</v>
+        <v>2.5372</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3463</v>
+        <v>2.4201</v>
       </c>
       <c r="G3" t="n">
         <v>1.2571</v>
@@ -688,13 +688,13 @@
         <v>3.1499</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2689</v>
+        <v>-0.5413</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7996</v>
+        <v>-0.1458</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4693</v>
+        <v>-0.3955</v>
       </c>
       <c r="V3" t="n">
         <v>2.2033</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3334</v>
+        <v>2.9165</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6998</v>
+        <v>2.429</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.4875</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3104</v>
+        <v>3.4147</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5976</v>
+        <v>0.2768</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7128</v>
+        <v>3.1379</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8865</v>
+        <v>3.3187</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8036</v>
+        <v>0.5495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0829</v>
+        <v>2.7691</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4239</v>
+        <v>0.096</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.206</v>
+        <v>-0.2727</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6299</v>
+        <v>0.3687</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.07190000000000001</v>
+        <v>0.1486</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8133</v>
+        <v>0.222</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8852</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9433</v>
+        <v>-1.5733</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9433</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0529</v>
+        <v>2.8251</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8056</v>
+        <v>2.167</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2473</v>
+        <v>0.6582</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0755</v>
+        <v>2.3104</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7759</v>
+        <v>1.5976</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2996</v>
+        <v>0.7128</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8342</v>
+        <v>1.8865</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8803</v>
+        <v>1.8036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9538</v>
+        <v>0.0829</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2413</v>
+        <v>0.4239</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1044</v>
+        <v>-0.206</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3457</v>
+        <v>0.6299</v>
       </c>
       <c r="P5" t="n">
-        <v>1.297</v>
+        <v>2.0382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9381</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1567</v>
+        <v>0.2804</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7814</v>
+        <v>-0.8605</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2578</v>
+        <v>-0.9433</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2578</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4883</v>
+        <v>2.683</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4883</v>
+        <v>1.6327</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.0503</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4883</v>
+        <v>2.0755</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.7759</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4883</v>
+        <v>1.2996</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4883</v>
+        <v>1.8342</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.8803</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4883</v>
+        <v>0.9538</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.2413</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.1044</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.3457</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.5683</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0161</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.5844</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2578</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CASAS GARCIA</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1131</v>
+        <v>2.4883</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7015</v>
+        <v>2.4883</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4115</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2491</v>
+        <v>2.4883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9465</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3026</v>
+        <v>2.4883</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0721</v>
+        <v>2.4883</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0306</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0415</v>
+        <v>2.4883</v>
       </c>
       <c r="M7" t="n">
-        <v>0.177</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08409999999999999</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2611</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>S. CASAS GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8337</v>
+        <v>2.1869</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5678</v>
+        <v>1.7015</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2659</v>
+        <v>0.4854</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4147</v>
+        <v>1.2491</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2768</v>
+        <v>0.9465</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1379</v>
+        <v>0.3026</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3187</v>
+        <v>1.0721</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5495</v>
+        <v>1.0306</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7691</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>0.096</v>
+        <v>0.177</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2727</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3687</v>
+        <v>0.2611</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9264</v>
+        <v>0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0382</v>
+        <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9341</v>
+        <v>0.1231</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6392</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.295</v>
+        <v>0.1231</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5733</v>
+        <v>0.6294</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3736</v>
+        <v>1.1547</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.7198</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3669</v>
+        <v>1.8745</v>
       </c>
       <c r="G9" t="n">
         <v>1.8032</v>
@@ -1156,13 +1156,13 @@
         <v>2.7793</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4041</v>
+        <v>0.1853</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0684</v>
+        <v>0.342</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3357</v>
+        <v>-0.1567</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5749</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4317</v>
+        <v>0.2696</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0703</v>
+        <v>-2.1355</v>
       </c>
       <c r="F10" t="n">
-        <v>0.502</v>
+        <v>2.405</v>
       </c>
       <c r="G10" t="n">
-        <v>0.801</v>
+        <v>3.2191</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2664</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5346</v>
+        <v>3.3177</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2355</v>
+        <v>2.7166</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8931</v>
+        <v>-0.1248</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3425</v>
+        <v>2.8414</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4345</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6267</v>
+        <v>0.0262</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1922</v>
+        <v>0.4763</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3706</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>-3.891</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4087</v>
+        <v>2.0382</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5746</v>
+        <v>-0.4666</v>
       </c>
       <c r="T10" t="n">
-        <v>1.159</v>
+        <v>-0.3311</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4156</v>
+        <v>-0.1356</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5733</v>
+        <v>-0.63</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.1571</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1948</v>
+        <v>0.163</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.203</v>
+        <v>-0.006</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8754999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1823</v>
+        <v>0.3476</v>
       </c>
       <c r="T11" t="n">
-        <v>0.051</v>
+        <v>0.0193</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1313</v>
+        <v>0.3283</v>
       </c>
       <c r="V11" t="n">
         <v>0.3144</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.428</v>
+        <v>-0.5618</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7345</v>
+        <v>-0.8423</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3066</v>
+        <v>0.2804</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2191</v>
+        <v>0.801</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.2664</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3177</v>
+        <v>0.5346</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7166</v>
+        <v>1.2355</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1248</v>
+        <v>0.8931</v>
       </c>
       <c r="L12" t="n">
-        <v>2.8414</v>
+        <v>0.3425</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5024999999999999</v>
+        <v>-0.4345</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0262</v>
+        <v>-0.6267</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4763</v>
+        <v>0.1922</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8529</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.891</v>
+        <v>-2.7793</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0382</v>
+        <v>2.4087</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1642</v>
+        <v>0.581</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9302</v>
+        <v>0.3871</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2341</v>
+        <v>0.194</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.63</v>
+        <v>-1.5733</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0452</v>
+        <v>-0.9198</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0252</v>
+        <v>-1.0229</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.02</v>
+        <v>0.1031</v>
       </c>
       <c r="G13" t="n">
         <v>-0.056</v>
@@ -1468,13 +1468,13 @@
         <v>2.594</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1391</v>
+        <v>-0.0137</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.909</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2301</v>
+        <v>-0.107</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5177</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.1277</v>
+        <v>28.769</v>
       </c>
       <c r="E14" t="n">
-        <v>13.7681</v>
+        <v>15.4094</v>
       </c>
       <c r="F14" t="n">
-        <v>13.3595</v>
+        <v>13.3594</v>
       </c>
       <c r="G14" t="n">
         <v>25.9863</v>
@@ -1546,13 +1546,13 @@
         <v>22.2346</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1265</v>
+        <v>-0.4850000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7087</v>
+        <v>0.9328999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.418</v>
+        <v>-1.4179</v>
       </c>
       <c r="V14" t="n">
         <v>-6.9232</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0378</v>
+        <v>2.7996</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0652</v>
+        <v>2.9672</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0274</v>
+        <v>-0.1676</v>
       </c>
       <c r="G15" t="n">
         <v>1.3301</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5753</v>
+        <v>1.3371</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9949</v>
+        <v>0.8969</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5805</v>
+        <v>0.4402</v>
       </c>
       <c r="V15" t="n">
         <v>0.503</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.981</v>
+        <v>-1.1276</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2143</v>
+        <v>-1.4102</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2333</v>
+        <v>0.2825</v>
       </c>
       <c r="G17" t="n">
         <v>-2.068</v>
@@ -1780,13 +1780,13 @@
         <v>0.1853</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2728</v>
+        <v>0.1262</v>
       </c>
       <c r="T17" t="n">
-        <v>0.051</v>
+        <v>-0.1449</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2218</v>
+        <v>0.2711</v>
       </c>
       <c r="V17" t="n">
         <v>0.6289</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4553</v>
+        <v>-1.5783</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4883</v>
+        <v>1.4696</v>
       </c>
       <c r="F19" t="n">
-        <v>0.033</v>
+        <v>-3.0479</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.9159</v>
+        <v>-2.4251</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8134</v>
+        <v>-0.9198</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1025</v>
+        <v>-1.5053</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3687</v>
+        <v>-0.5629</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.4101</v>
+        <v>0.7428</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0415</v>
+        <v>-1.3057</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5472</v>
+        <v>-1.8621</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4033</v>
+        <v>-1.6626</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.144</v>
+        <v>-0.1996</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9646</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7745</v>
+        <v>0.8991</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8096</v>
+        <v>0.1269</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9649</v>
+        <v>0.7722</v>
       </c>
       <c r="V19" t="n">
-        <v>3.6507</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>3.7766</v>
+        <v>2.8321</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1259</v>
+        <v>-2.3286</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6596</v>
+        <v>-2.3796</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4696</v>
+        <v>-2.1738</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1292</v>
+        <v>-0.2058</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4251</v>
+        <v>-3.9159</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9198</v>
+        <v>-2.8134</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5053</v>
+        <v>-1.1025</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5629</v>
+        <v>-2.3687</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7428</v>
+        <v>-2.4101</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3057</v>
+        <v>0.0415</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8621</v>
+        <v>-1.5472</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6626</v>
+        <v>-0.4033</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1996</v>
+        <v>-1.144</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-2.9646</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8177</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1269</v>
+        <v>0.1241</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6909</v>
+        <v>0.7262</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5034999999999999</v>
+        <v>3.6507</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8321</v>
+        <v>3.7766</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3286</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5621</v>
+        <v>-3.3914</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8397</v>
+        <v>-1.5459</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7224</v>
+        <v>-1.8455</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5168</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0485</v>
+        <v>0.1222</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0174</v>
+        <v>0.3112</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0659</v>
+        <v>-0.189</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0703</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>P. SECO LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5428</v>
+        <v>-4.3091</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.205</v>
+        <v>-3.3816</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3378</v>
+        <v>-0.9275</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0243</v>
+        <v>-0.4801</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7525</v>
+        <v>1.2523</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2719</v>
+        <v>-1.7324</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2002</v>
+        <v>1.8189</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3221</v>
+        <v>2.4303</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1219</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.2245</v>
+        <v>-2.2989</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0745</v>
+        <v>-1.178</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.15</v>
+        <v>-1.121</v>
       </c>
       <c r="P22" t="n">
+        <v>-5.9292</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-6.485</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.5558999999999999</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.8529</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.4087</v>
-      </c>
       <c r="S22" t="n">
-        <v>0.3104</v>
+        <v>-0.4181</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4477</v>
+        <v>-0.2888</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1373</v>
+        <v>-0.1294</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3847</v>
+        <v>2.5183</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3847</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. CORREA GALLARDO</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.989</v>
+        <v>-4.3384</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5522</v>
+        <v>-1.205</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4368</v>
+        <v>-3.1334</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.9347</v>
+        <v>-4.0243</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3282</v>
+        <v>-1.7525</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.6066</v>
+        <v>-2.2719</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9466</v>
+        <v>0.2002</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1932</v>
+        <v>0.3221</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.1399</v>
+        <v>-0.1219</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.9881</v>
+        <v>-4.2245</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.5214</v>
+        <v>-2.0745</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4667</v>
+        <v>-2.15</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8529</v>
+        <v>2.4087</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8521</v>
+        <v>0.5148</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6056</v>
+        <v>0.4477</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2465</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0.945</v>
+        <v>-1.3847</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.945</v>
+        <v>-1.3847</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. SECO LOPEZ</t>
+          <t>P. CORREA GALLARDO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0793</v>
+        <v>-4.4988</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4796</v>
+        <v>-3.1605</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5997</v>
+        <v>-1.3383</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4801</v>
+        <v>-6.9347</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2523</v>
+        <v>-2.3282</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7324</v>
+        <v>-4.6066</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8189</v>
+        <v>-2.9466</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4303</v>
+        <v>0.1932</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-3.1399</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2989</v>
+        <v>-3.9881</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.178</v>
+        <v>-2.5214</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.121</v>
+        <v>-1.4667</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.9292</v>
+        <v>1.8529</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.485</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1883</v>
+        <v>-0.3619</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3867</v>
+        <v>-0.2139</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8016</v>
+        <v>-0.148</v>
       </c>
       <c r="V24" t="n">
-        <v>2.5183</v>
+        <v>0.945</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0.945</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.6388</v>
+        <v>-7.3937</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9167</v>
+        <v>-5.7208</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7221</v>
+        <v>-1.6729</v>
       </c>
       <c r="G25" t="n">
         <v>-5.8582</v>
@@ -2404,13 +2404,13 @@
         <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3713</v>
+        <v>-0.1262</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1269</v>
+        <v>0.3227</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4982</v>
+        <v>-0.4489</v>
       </c>
       <c r="V25" t="n">
         <v>0.6289</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-27.1275</v>
+        <v>-26.4747</v>
       </c>
       <c r="E26" t="n">
         <v>-13.3596</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.768</v>
+        <v>-13.1153</v>
       </c>
       <c r="G26" t="n">
         <v>-25.9863</v>
@@ -2482,13 +2482,13 @@
         <v>12.0437</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1264</v>
+        <v>2.7794</v>
       </c>
       <c r="T26" t="n">
-        <v>1.418</v>
+        <v>1.4178</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7085999999999999</v>
+        <v>1.3615</v>
       </c>
       <c r="V26" t="n">
         <v>6.923299999999999</v>
@@ -2497,7 +2497,7 @@
         <v>9.7532</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.829899999999999</v>
+        <v>-2.8299</v>
       </c>
     </row>
   </sheetData>
